--- a/Award/第十届教育部人文社科奖.xlsx
+++ b/Award/第十届教育部人文社科奖.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zhen\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\Award\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DE9183-2211-465C-A7EA-67BBE38FA08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5025E954-8354-4C10-B4AC-3F96625B9489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$1493</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7480" uniqueCount="3007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7480" uniqueCount="3005">
   <si>
     <t>申报成果名称</t>
   </si>
@@ -8726,14 +8726,6 @@
   </si>
   <si>
     <t>普及读物</t>
-  </si>
-  <si>
-    <t>咨询服
-务报告</t>
-  </si>
-  <si>
-    <t>普及读
-物</t>
   </si>
   <si>
     <t>青年成果奖</t>
@@ -9466,7 +9458,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2904</v>
+        <v>2902</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -9609,7 +9601,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>2905</v>
+        <v>2903</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1385</v>
@@ -10110,7 +10102,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>2906</v>
+        <v>2904</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>1386</v>
@@ -10490,7 +10482,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>2907</v>
+        <v>2905</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>1385</v>
@@ -10950,7 +10942,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>2908</v>
+        <v>2906</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>1386</v>
@@ -12790,7 +12782,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>2909</v>
+        <v>2907</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>1386</v>
@@ -12890,7 +12882,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>2910</v>
+        <v>2908</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>1386</v>
@@ -13210,7 +13202,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>2911</v>
+        <v>2909</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>1385</v>
@@ -13290,7 +13282,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>2912</v>
+        <v>2910</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>1386</v>
@@ -13430,7 +13422,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>2913</v>
+        <v>2911</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>1385</v>
@@ -13530,7 +13522,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>2914</v>
+        <v>2912</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>1386</v>
@@ -13650,7 +13642,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>2915</v>
+        <v>2913</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>1385</v>
@@ -13670,7 +13662,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>2916</v>
+        <v>2914</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>1386</v>
@@ -13930,7 +13922,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>2917</v>
+        <v>2915</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>1386</v>
@@ -14030,7 +14022,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>2918</v>
+        <v>2916</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>1386</v>
@@ -15550,7 +15542,7 @@
         <v>304</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>2919</v>
+        <v>2917</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>1386</v>
@@ -15610,7 +15602,7 @@
         <v>307</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>2920</v>
+        <v>2918</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>1386</v>
@@ -15650,7 +15642,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>2921</v>
+        <v>2919</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>1386</v>
@@ -16590,7 +16582,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>2922</v>
+        <v>2920</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>1386</v>
@@ -17150,7 +17142,7 @@
         <v>384</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>2923</v>
+        <v>2921</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>1385</v>
@@ -18770,7 +18762,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>2924</v>
+        <v>2922</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>1386</v>
@@ -18810,7 +18802,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="5" t="s">
-        <v>2925</v>
+        <v>2923</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>1386</v>
@@ -18930,7 +18922,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="5" t="s">
-        <v>2926</v>
+        <v>2924</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>1386</v>
@@ -19050,7 +19042,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="5" t="s">
-        <v>2927</v>
+        <v>2925</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>1386</v>
@@ -19070,7 +19062,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="5" t="s">
-        <v>2928</v>
+        <v>2926</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>1386</v>
@@ -19170,7 +19162,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="5" t="s">
-        <v>2929</v>
+        <v>2927</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>1385</v>
@@ -19230,7 +19222,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="5" t="s">
-        <v>2930</v>
+        <v>2928</v>
       </c>
       <c r="C489" s="1" t="s">
         <v>1386</v>
@@ -19250,7 +19242,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>2931</v>
+        <v>2929</v>
       </c>
       <c r="C490" s="1" t="s">
         <v>1386</v>
@@ -19370,7 +19362,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="5" t="s">
-        <v>2932</v>
+        <v>2930</v>
       </c>
       <c r="C496" s="1" t="s">
         <v>1386</v>
@@ -19410,7 +19402,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="5" t="s">
-        <v>2933</v>
+        <v>2931</v>
       </c>
       <c r="C498" s="1" t="s">
         <v>1386</v>
@@ -19450,7 +19442,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="5" t="s">
-        <v>2934</v>
+        <v>2932</v>
       </c>
       <c r="C500" s="1" t="s">
         <v>1386</v>
@@ -19510,7 +19502,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="5" t="s">
-        <v>2935</v>
+        <v>2933</v>
       </c>
       <c r="C503" s="1" t="s">
         <v>1386</v>
@@ -19570,7 +19562,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="5" t="s">
-        <v>2936</v>
+        <v>2934</v>
       </c>
       <c r="C506" s="1" t="s">
         <v>1386</v>
@@ -19830,7 +19822,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="5" t="s">
-        <v>2937</v>
+        <v>2935</v>
       </c>
       <c r="C519" s="1" t="s">
         <v>1386</v>
@@ -19930,7 +19922,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="5" t="s">
-        <v>2938</v>
+        <v>2936</v>
       </c>
       <c r="C524" s="1" t="s">
         <v>1386</v>
@@ -20090,7 +20082,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="5" t="s">
-        <v>2939</v>
+        <v>2937</v>
       </c>
       <c r="C532" s="1" t="s">
         <v>1386</v>
@@ -20190,7 +20182,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="5" t="s">
-        <v>2940</v>
+        <v>2938</v>
       </c>
       <c r="C537" s="1" t="s">
         <v>1386</v>
@@ -20410,7 +20402,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="5" t="s">
-        <v>2941</v>
+        <v>2939</v>
       </c>
       <c r="C548" s="1" t="s">
         <v>1386</v>
@@ -21130,7 +21122,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="5" t="s">
-        <v>2942</v>
+        <v>2940</v>
       </c>
       <c r="C584" s="1" t="s">
         <v>1385</v>
@@ -21250,7 +21242,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="5" t="s">
-        <v>2943</v>
+        <v>2941</v>
       </c>
       <c r="C590" s="1" t="s">
         <v>1386</v>
@@ -23290,7 +23282,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="5" t="s">
-        <v>2944</v>
+        <v>2942</v>
       </c>
       <c r="C692" s="1" t="s">
         <v>1386</v>
@@ -23590,7 +23582,7 @@
         <v>706</v>
       </c>
       <c r="B707" s="5" t="s">
-        <v>2945</v>
+        <v>2943</v>
       </c>
       <c r="C707" s="1" t="s">
         <v>1386</v>
@@ -23670,7 +23662,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="5" t="s">
-        <v>2946</v>
+        <v>2944</v>
       </c>
       <c r="C711" s="1" t="s">
         <v>1386</v>
@@ -23890,7 +23882,7 @@
         <v>721</v>
       </c>
       <c r="B722" s="5" t="s">
-        <v>2947</v>
+        <v>2945</v>
       </c>
       <c r="C722" s="1" t="s">
         <v>1386</v>
@@ -24130,7 +24122,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="5" t="s">
-        <v>2948</v>
+        <v>2946</v>
       </c>
       <c r="C734" s="1" t="s">
         <v>1386</v>
@@ -24190,7 +24182,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="5" t="s">
-        <v>2949</v>
+        <v>2947</v>
       </c>
       <c r="C737" s="1" t="s">
         <v>1385</v>
@@ -24450,7 +24442,7 @@
         <v>749</v>
       </c>
       <c r="B750" s="5" t="s">
-        <v>2950</v>
+        <v>2948</v>
       </c>
       <c r="C750" s="1" t="s">
         <v>1386</v>
@@ -25010,7 +25002,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="5" t="s">
-        <v>2951</v>
+        <v>2949</v>
       </c>
       <c r="C778" s="1" t="s">
         <v>1386</v>
@@ -26150,7 +26142,7 @@
         <v>834</v>
       </c>
       <c r="B835" s="5" t="s">
-        <v>2952</v>
+        <v>2950</v>
       </c>
       <c r="C835" s="1" t="s">
         <v>1386</v>
@@ -26230,7 +26222,7 @@
         <v>838</v>
       </c>
       <c r="B839" s="5" t="s">
-        <v>2953</v>
+        <v>2951</v>
       </c>
       <c r="C839" s="1" t="s">
         <v>1386</v>
@@ -26290,7 +26282,7 @@
         <v>841</v>
       </c>
       <c r="B842" s="5" t="s">
-        <v>2954</v>
+        <v>2952</v>
       </c>
       <c r="C842" s="1" t="s">
         <v>1386</v>
@@ -28150,7 +28142,7 @@
         <v>934</v>
       </c>
       <c r="B935" s="5" t="s">
-        <v>2955</v>
+        <v>2953</v>
       </c>
       <c r="C935" s="1" t="s">
         <v>1385</v>
@@ -28350,7 +28342,7 @@
         <v>944</v>
       </c>
       <c r="B945" s="5" t="s">
-        <v>2956</v>
+        <v>2954</v>
       </c>
       <c r="C945" s="1" t="s">
         <v>1386</v>
@@ -29350,7 +29342,7 @@
         <v>994</v>
       </c>
       <c r="B995" s="5" t="s">
-        <v>2957</v>
+        <v>2955</v>
       </c>
       <c r="C995" s="1" t="s">
         <v>1386</v>
@@ -29810,7 +29802,7 @@
         <v>1017</v>
       </c>
       <c r="B1018" s="5" t="s">
-        <v>2958</v>
+        <v>2956</v>
       </c>
       <c r="C1018" s="1" t="s">
         <v>1386</v>
@@ -29830,7 +29822,7 @@
         <v>1018</v>
       </c>
       <c r="B1019" s="5" t="s">
-        <v>2959</v>
+        <v>2957</v>
       </c>
       <c r="C1019" s="1" t="s">
         <v>1386</v>
@@ -29870,7 +29862,7 @@
         <v>1020</v>
       </c>
       <c r="B1021" s="5" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
       <c r="C1021" s="1" t="s">
         <v>1386</v>
@@ -29910,7 +29902,7 @@
         <v>1022</v>
       </c>
       <c r="B1023" s="5" t="s">
-        <v>2961</v>
+        <v>2959</v>
       </c>
       <c r="C1023" s="1" t="s">
         <v>1386</v>
@@ -29950,7 +29942,7 @@
         <v>1024</v>
       </c>
       <c r="B1025" s="5" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="C1025" s="1" t="s">
         <v>1386</v>
@@ -29990,7 +29982,7 @@
         <v>1026</v>
       </c>
       <c r="B1027" s="5" t="s">
-        <v>2963</v>
+        <v>2961</v>
       </c>
       <c r="C1027" s="1" t="s">
         <v>1386</v>
@@ -30110,7 +30102,7 @@
         <v>1032</v>
       </c>
       <c r="B1033" s="5" t="s">
-        <v>2964</v>
+        <v>2962</v>
       </c>
       <c r="C1033" s="1" t="s">
         <v>1386</v>
@@ -30130,7 +30122,7 @@
         <v>1033</v>
       </c>
       <c r="B1034" s="5" t="s">
-        <v>2965</v>
+        <v>2963</v>
       </c>
       <c r="C1034" s="1" t="s">
         <v>1386</v>
@@ -30170,7 +30162,7 @@
         <v>1035</v>
       </c>
       <c r="B1036" s="5" t="s">
-        <v>2966</v>
+        <v>2964</v>
       </c>
       <c r="C1036" s="1" t="s">
         <v>1386</v>
@@ -30310,7 +30302,7 @@
         <v>1042</v>
       </c>
       <c r="B1043" s="5" t="s">
-        <v>2967</v>
+        <v>2965</v>
       </c>
       <c r="C1043" s="1" t="s">
         <v>1386</v>
@@ -30470,7 +30462,7 @@
         <v>1050</v>
       </c>
       <c r="B1051" s="5" t="s">
-        <v>2968</v>
+        <v>2966</v>
       </c>
       <c r="C1051" s="1" t="s">
         <v>1386</v>
@@ -30550,7 +30542,7 @@
         <v>1054</v>
       </c>
       <c r="B1055" s="5" t="s">
-        <v>2969</v>
+        <v>2967</v>
       </c>
       <c r="C1055" s="1" t="s">
         <v>1386</v>
@@ -30650,7 +30642,7 @@
         <v>1059</v>
       </c>
       <c r="B1060" s="5" t="s">
-        <v>2970</v>
+        <v>2968</v>
       </c>
       <c r="C1060" s="1" t="s">
         <v>1386</v>
@@ -30690,7 +30682,7 @@
         <v>1061</v>
       </c>
       <c r="B1062" s="5" t="s">
-        <v>2971</v>
+        <v>2969</v>
       </c>
       <c r="C1062" s="1" t="s">
         <v>1385</v>
@@ -30730,7 +30722,7 @@
         <v>1063</v>
       </c>
       <c r="B1064" s="5" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="C1064" s="1" t="s">
         <v>1386</v>
@@ -30790,7 +30782,7 @@
         <v>1066</v>
       </c>
       <c r="B1067" s="5" t="s">
-        <v>2973</v>
+        <v>2971</v>
       </c>
       <c r="C1067" s="1" t="s">
         <v>1386</v>
@@ -30810,7 +30802,7 @@
         <v>1067</v>
       </c>
       <c r="B1068" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="C1068" s="1" t="s">
         <v>1386</v>
@@ -30850,7 +30842,7 @@
         <v>1069</v>
       </c>
       <c r="B1070" s="5" t="s">
-        <v>2975</v>
+        <v>2973</v>
       </c>
       <c r="C1070" s="1" t="s">
         <v>1385</v>
@@ -31010,7 +31002,7 @@
         <v>1077</v>
       </c>
       <c r="B1078" s="5" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="C1078" s="1" t="s">
         <v>1386</v>
@@ -31130,7 +31122,7 @@
         <v>1083</v>
       </c>
       <c r="B1084" s="5" t="s">
-        <v>2977</v>
+        <v>2975</v>
       </c>
       <c r="C1084" s="1" t="s">
         <v>1386</v>
@@ -31190,7 +31182,7 @@
         <v>1086</v>
       </c>
       <c r="B1087" s="5" t="s">
-        <v>2978</v>
+        <v>2976</v>
       </c>
       <c r="C1087" s="1" t="s">
         <v>1386</v>
@@ -31410,7 +31402,7 @@
         <v>1097</v>
       </c>
       <c r="B1098" s="5" t="s">
-        <v>2979</v>
+        <v>2977</v>
       </c>
       <c r="C1098" s="1" t="s">
         <v>1386</v>
@@ -31610,7 +31602,7 @@
         <v>1107</v>
       </c>
       <c r="B1108" s="5" t="s">
-        <v>2980</v>
+        <v>2978</v>
       </c>
       <c r="C1108" s="1" t="s">
         <v>1385</v>
@@ -31990,7 +31982,7 @@
         <v>1126</v>
       </c>
       <c r="B1127" s="5" t="s">
-        <v>2981</v>
+        <v>2979</v>
       </c>
       <c r="C1127" s="1" t="s">
         <v>1385</v>
@@ -33810,7 +33802,7 @@
         <v>1217</v>
       </c>
       <c r="B1218" s="5" t="s">
-        <v>2982</v>
+        <v>2980</v>
       </c>
       <c r="C1218" s="1" t="s">
         <v>1387</v>
@@ -35304,7 +35296,7 @@
         <v>2697</v>
       </c>
       <c r="F1290" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1291" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35324,7 +35316,7 @@
         <v>2698</v>
       </c>
       <c r="F1291" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1292" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35344,7 +35336,7 @@
         <v>2699</v>
       </c>
       <c r="F1292" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1293" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35364,7 +35356,7 @@
         <v>2700</v>
       </c>
       <c r="F1293" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1294" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35384,7 +35376,7 @@
         <v>2701</v>
       </c>
       <c r="F1294" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1295" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35404,7 +35396,7 @@
         <v>2702</v>
       </c>
       <c r="F1295" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1296" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35424,7 +35416,7 @@
         <v>2703</v>
       </c>
       <c r="F1296" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1297" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35444,7 +35436,7 @@
         <v>2704</v>
       </c>
       <c r="F1297" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1298" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35464,7 +35456,7 @@
         <v>2705</v>
       </c>
       <c r="F1298" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1299" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35484,7 +35476,7 @@
         <v>2706</v>
       </c>
       <c r="F1299" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1300" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35504,7 +35496,7 @@
         <v>2707</v>
       </c>
       <c r="F1300" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1301" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35524,7 +35516,7 @@
         <v>2708</v>
       </c>
       <c r="F1301" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1302" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35544,7 +35536,7 @@
         <v>2709</v>
       </c>
       <c r="F1302" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1303" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35564,7 +35556,7 @@
         <v>2710</v>
       </c>
       <c r="F1303" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1304" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35584,7 +35576,7 @@
         <v>2711</v>
       </c>
       <c r="F1304" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1305" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35604,7 +35596,7 @@
         <v>2712</v>
       </c>
       <c r="F1305" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1306" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35624,7 +35616,7 @@
         <v>2713</v>
       </c>
       <c r="F1306" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1307" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35644,7 +35636,7 @@
         <v>2714</v>
       </c>
       <c r="F1307" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1308" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35664,7 +35656,7 @@
         <v>2715</v>
       </c>
       <c r="F1308" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1309" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35684,7 +35676,7 @@
         <v>2716</v>
       </c>
       <c r="F1309" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1310" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35704,7 +35696,7 @@
         <v>2717</v>
       </c>
       <c r="F1310" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1311" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35724,7 +35716,7 @@
         <v>2718</v>
       </c>
       <c r="F1311" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1312" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35744,7 +35736,7 @@
         <v>2719</v>
       </c>
       <c r="F1312" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1313" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35764,7 +35756,7 @@
         <v>2720</v>
       </c>
       <c r="F1313" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1314" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35784,7 +35776,7 @@
         <v>2721</v>
       </c>
       <c r="F1314" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1315" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35804,7 +35796,7 @@
         <v>2722</v>
       </c>
       <c r="F1315" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1316" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35824,7 +35816,7 @@
         <v>2723</v>
       </c>
       <c r="F1316" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1317" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35844,7 +35836,7 @@
         <v>2724</v>
       </c>
       <c r="F1317" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1318" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35864,7 +35856,7 @@
         <v>2725</v>
       </c>
       <c r="F1318" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1319" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35872,7 +35864,7 @@
         <v>1318</v>
       </c>
       <c r="B1319" s="5" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="C1319" s="1" t="s">
         <v>1386</v>
@@ -35884,7 +35876,7 @@
         <v>2726</v>
       </c>
       <c r="F1319" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1320" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35892,7 +35884,7 @@
         <v>1319</v>
       </c>
       <c r="B1320" s="5" t="s">
-        <v>2984</v>
+        <v>2982</v>
       </c>
       <c r="C1320" s="1" t="s">
         <v>1386</v>
@@ -35904,7 +35896,7 @@
         <v>2727</v>
       </c>
       <c r="F1320" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1321" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35924,7 +35916,7 @@
         <v>2728</v>
       </c>
       <c r="F1321" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1322" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35932,7 +35924,7 @@
         <v>1321</v>
       </c>
       <c r="B1322" s="5" t="s">
-        <v>2985</v>
+        <v>2983</v>
       </c>
       <c r="C1322" s="1" t="s">
         <v>1386</v>
@@ -35944,7 +35936,7 @@
         <v>2729</v>
       </c>
       <c r="F1322" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1323" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35964,7 +35956,7 @@
         <v>2730</v>
       </c>
       <c r="F1323" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1324" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35984,7 +35976,7 @@
         <v>2731</v>
       </c>
       <c r="F1324" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1325" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36004,7 +35996,7 @@
         <v>2732</v>
       </c>
       <c r="F1325" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1326" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36024,7 +36016,7 @@
         <v>2733</v>
       </c>
       <c r="F1326" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1327" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36032,7 +36024,7 @@
         <v>1326</v>
       </c>
       <c r="B1327" s="5" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="C1327" s="1" t="s">
         <v>1386</v>
@@ -36044,7 +36036,7 @@
         <v>2734</v>
       </c>
       <c r="F1327" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1328" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36064,7 +36056,7 @@
         <v>2735</v>
       </c>
       <c r="F1328" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1329" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36084,7 +36076,7 @@
         <v>2736</v>
       </c>
       <c r="F1329" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1330" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36104,7 +36096,7 @@
         <v>2737</v>
       </c>
       <c r="F1330" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1331" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36124,7 +36116,7 @@
         <v>2738</v>
       </c>
       <c r="F1331" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1332" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36144,7 +36136,7 @@
         <v>2739</v>
       </c>
       <c r="F1332" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1333" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36164,7 +36156,7 @@
         <v>2740</v>
       </c>
       <c r="F1333" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1334" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36184,7 +36176,7 @@
         <v>2134</v>
       </c>
       <c r="F1334" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1335" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36204,7 +36196,7 @@
         <v>2741</v>
       </c>
       <c r="F1335" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1336" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36224,7 +36216,7 @@
         <v>2742</v>
       </c>
       <c r="F1336" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1337" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36244,7 +36236,7 @@
         <v>2743</v>
       </c>
       <c r="F1337" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1338" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36264,7 +36256,7 @@
         <v>2744</v>
       </c>
       <c r="F1338" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1339" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36284,7 +36276,7 @@
         <v>2745</v>
       </c>
       <c r="F1339" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1340" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36304,7 +36296,7 @@
         <v>2746</v>
       </c>
       <c r="F1340" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1341" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36324,7 +36316,7 @@
         <v>2747</v>
       </c>
       <c r="F1341" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1342" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36332,7 +36324,7 @@
         <v>1341</v>
       </c>
       <c r="B1342" s="5" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="C1342" s="1" t="s">
         <v>1385</v>
@@ -36344,7 +36336,7 @@
         <v>2748</v>
       </c>
       <c r="F1342" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1343" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36352,7 +36344,7 @@
         <v>1342</v>
       </c>
       <c r="B1343" s="5" t="s">
-        <v>2988</v>
+        <v>2986</v>
       </c>
       <c r="C1343" s="1" t="s">
         <v>1385</v>
@@ -36364,7 +36356,7 @@
         <v>2749</v>
       </c>
       <c r="F1343" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1344" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36384,7 +36376,7 @@
         <v>2750</v>
       </c>
       <c r="F1344" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1345" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36404,7 +36396,7 @@
         <v>2751</v>
       </c>
       <c r="F1345" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1346" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36424,7 +36416,7 @@
         <v>2752</v>
       </c>
       <c r="F1346" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1347" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36444,7 +36436,7 @@
         <v>2753</v>
       </c>
       <c r="F1347" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1348" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36464,7 +36456,7 @@
         <v>2754</v>
       </c>
       <c r="F1348" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1349" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36484,7 +36476,7 @@
         <v>2755</v>
       </c>
       <c r="F1349" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1350" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36504,7 +36496,7 @@
         <v>2756</v>
       </c>
       <c r="F1350" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1351" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36524,7 +36516,7 @@
         <v>2757</v>
       </c>
       <c r="F1351" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1352" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36544,7 +36536,7 @@
         <v>2758</v>
       </c>
       <c r="F1352" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1353" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36552,7 +36544,7 @@
         <v>1352</v>
       </c>
       <c r="B1353" s="5" t="s">
-        <v>2989</v>
+        <v>2987</v>
       </c>
       <c r="C1353" s="1" t="s">
         <v>1386</v>
@@ -36564,7 +36556,7 @@
         <v>2759</v>
       </c>
       <c r="F1353" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1354" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36584,7 +36576,7 @@
         <v>2760</v>
       </c>
       <c r="F1354" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1355" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36604,7 +36596,7 @@
         <v>2761</v>
       </c>
       <c r="F1355" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1356" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36624,7 +36616,7 @@
         <v>2762</v>
       </c>
       <c r="F1356" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1357" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36644,7 +36636,7 @@
         <v>2763</v>
       </c>
       <c r="F1357" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1358" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36664,7 +36656,7 @@
         <v>2764</v>
       </c>
       <c r="F1358" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1359" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36684,7 +36676,7 @@
         <v>2169</v>
       </c>
       <c r="F1359" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1360" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36692,7 +36684,7 @@
         <v>1359</v>
       </c>
       <c r="B1360" s="5" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="C1360" s="1" t="s">
         <v>1386</v>
@@ -36704,7 +36696,7 @@
         <v>2765</v>
       </c>
       <c r="F1360" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1361" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36724,7 +36716,7 @@
         <v>2766</v>
       </c>
       <c r="F1361" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1362" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36732,7 +36724,7 @@
         <v>1361</v>
       </c>
       <c r="B1362" s="5" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
       <c r="C1362" s="1" t="s">
         <v>1386</v>
@@ -36744,7 +36736,7 @@
         <v>2593</v>
       </c>
       <c r="F1362" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1363" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36764,7 +36756,7 @@
         <v>2767</v>
       </c>
       <c r="F1363" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1364" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36784,7 +36776,7 @@
         <v>2768</v>
       </c>
       <c r="F1364" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1365" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36804,7 +36796,7 @@
         <v>2769</v>
       </c>
       <c r="F1365" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1366" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36824,7 +36816,7 @@
         <v>2759</v>
       </c>
       <c r="F1366" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1367" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36844,7 +36836,7 @@
         <v>2770</v>
       </c>
       <c r="F1367" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1368" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36864,7 +36856,7 @@
         <v>2771</v>
       </c>
       <c r="F1368" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1369" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36884,7 +36876,7 @@
         <v>2772</v>
       </c>
       <c r="F1369" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1370" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36904,7 +36896,7 @@
         <v>2773</v>
       </c>
       <c r="F1370" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1371" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36924,7 +36916,7 @@
         <v>2774</v>
       </c>
       <c r="F1371" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1372" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36944,7 +36936,7 @@
         <v>2775</v>
       </c>
       <c r="F1372" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1373" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36964,7 +36956,7 @@
         <v>2776</v>
       </c>
       <c r="F1373" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1374" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -36984,7 +36976,7 @@
         <v>2777</v>
       </c>
       <c r="F1374" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1375" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37004,7 +36996,7 @@
         <v>2778</v>
       </c>
       <c r="F1375" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1376" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37024,7 +37016,7 @@
         <v>2779</v>
       </c>
       <c r="F1376" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1377" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37044,7 +37036,7 @@
         <v>2780</v>
       </c>
       <c r="F1377" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1378" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37064,7 +37056,7 @@
         <v>2092</v>
       </c>
       <c r="F1378" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1379" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37084,7 +37076,7 @@
         <v>2781</v>
       </c>
       <c r="F1379" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1380" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37092,7 +37084,7 @@
         <v>1379</v>
       </c>
       <c r="B1380" s="5" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
       <c r="C1380" s="1" t="s">
         <v>1385</v>
@@ -37104,7 +37096,7 @@
         <v>2782</v>
       </c>
       <c r="F1380" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1381" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37124,7 +37116,7 @@
         <v>2783</v>
       </c>
       <c r="F1381" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1382" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37144,7 +37136,7 @@
         <v>2784</v>
       </c>
       <c r="F1382" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1383" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37164,7 +37156,7 @@
         <v>2785</v>
       </c>
       <c r="F1383" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1384" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37184,7 +37176,7 @@
         <v>2786</v>
       </c>
       <c r="F1384" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1385" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37204,7 +37196,7 @@
         <v>2787</v>
       </c>
       <c r="F1385" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1386" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37224,7 +37216,7 @@
         <v>2788</v>
       </c>
       <c r="F1386" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1387" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37232,7 +37224,7 @@
         <v>1386</v>
       </c>
       <c r="B1387" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
       <c r="C1387" s="1" t="s">
         <v>1385</v>
@@ -37244,7 +37236,7 @@
         <v>2789</v>
       </c>
       <c r="F1387" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1388" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37264,7 +37256,7 @@
         <v>2790</v>
       </c>
       <c r="F1388" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1389" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37284,7 +37276,7 @@
         <v>2791</v>
       </c>
       <c r="F1389" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1390" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37292,7 +37284,7 @@
         <v>1389</v>
       </c>
       <c r="B1390" s="5" t="s">
-        <v>2994</v>
+        <v>2992</v>
       </c>
       <c r="C1390" s="1" t="s">
         <v>1386</v>
@@ -37304,7 +37296,7 @@
         <v>2792</v>
       </c>
       <c r="F1390" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1391" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37324,7 +37316,7 @@
         <v>2793</v>
       </c>
       <c r="F1391" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1392" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37344,7 +37336,7 @@
         <v>2794</v>
       </c>
       <c r="F1392" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1393" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37364,7 +37356,7 @@
         <v>2795</v>
       </c>
       <c r="F1393" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1394" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37384,7 +37376,7 @@
         <v>2796</v>
       </c>
       <c r="F1394" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1395" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37404,7 +37396,7 @@
         <v>2797</v>
       </c>
       <c r="F1395" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1396" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37424,7 +37416,7 @@
         <v>2798</v>
       </c>
       <c r="F1396" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1397" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37444,7 +37436,7 @@
         <v>2799</v>
       </c>
       <c r="F1397" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1398" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37464,7 +37456,7 @@
         <v>2800</v>
       </c>
       <c r="F1398" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1399" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37484,7 +37476,7 @@
         <v>2801</v>
       </c>
       <c r="F1399" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1400" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37504,7 +37496,7 @@
         <v>2802</v>
       </c>
       <c r="F1400" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1401" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37524,7 +37516,7 @@
         <v>2803</v>
       </c>
       <c r="F1401" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1402" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37544,7 +37536,7 @@
         <v>2804</v>
       </c>
       <c r="F1402" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1403" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37564,7 +37556,7 @@
         <v>2805</v>
       </c>
       <c r="F1403" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1404" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37584,7 +37576,7 @@
         <v>2806</v>
       </c>
       <c r="F1404" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1405" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37604,7 +37596,7 @@
         <v>2807</v>
       </c>
       <c r="F1405" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1406" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37624,7 +37616,7 @@
         <v>2808</v>
       </c>
       <c r="F1406" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1407" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37644,7 +37636,7 @@
         <v>2809</v>
       </c>
       <c r="F1407" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1408" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37664,7 +37656,7 @@
         <v>2810</v>
       </c>
       <c r="F1408" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1409" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37684,7 +37676,7 @@
         <v>2811</v>
       </c>
       <c r="F1409" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1410" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37704,7 +37696,7 @@
         <v>2812</v>
       </c>
       <c r="F1410" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1411" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37724,7 +37716,7 @@
         <v>2813</v>
       </c>
       <c r="F1411" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1412" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37744,7 +37736,7 @@
         <v>2814</v>
       </c>
       <c r="F1412" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1413" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37764,7 +37756,7 @@
         <v>2815</v>
       </c>
       <c r="F1413" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1414" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37784,7 +37776,7 @@
         <v>2816</v>
       </c>
       <c r="F1414" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1415" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37804,7 +37796,7 @@
         <v>2817</v>
       </c>
       <c r="F1415" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1416" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37824,7 +37816,7 @@
         <v>2818</v>
       </c>
       <c r="F1416" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1417" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37844,7 +37836,7 @@
         <v>2819</v>
       </c>
       <c r="F1417" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1418" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37864,7 +37856,7 @@
         <v>2820</v>
       </c>
       <c r="F1418" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1419" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37884,7 +37876,7 @@
         <v>2821</v>
       </c>
       <c r="F1419" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1420" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37904,7 +37896,7 @@
         <v>2822</v>
       </c>
       <c r="F1420" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1421" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37924,7 +37916,7 @@
         <v>2823</v>
       </c>
       <c r="F1421" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1422" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37944,7 +37936,7 @@
         <v>2824</v>
       </c>
       <c r="F1422" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1423" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37955,7 +37947,7 @@
         <v>1326</v>
       </c>
       <c r="C1423" s="1" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="D1423" s="1" t="s">
         <v>1407</v>
@@ -37964,7 +37956,7 @@
         <v>2825</v>
       </c>
       <c r="F1423" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1424" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -37984,7 +37976,7 @@
         <v>2826</v>
       </c>
       <c r="F1424" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1425" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38004,7 +37996,7 @@
         <v>2827</v>
       </c>
       <c r="F1425" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1426" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38012,7 +38004,7 @@
         <v>1425</v>
       </c>
       <c r="B1426" s="5" t="s">
-        <v>2995</v>
+        <v>2993</v>
       </c>
       <c r="C1426" s="1" t="s">
         <v>1386</v>
@@ -38024,7 +38016,7 @@
         <v>2828</v>
       </c>
       <c r="F1426" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1427" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38032,7 +38024,7 @@
         <v>1426</v>
       </c>
       <c r="B1427" s="5" t="s">
-        <v>2996</v>
+        <v>2994</v>
       </c>
       <c r="C1427" s="1" t="s">
         <v>1386</v>
@@ -38044,7 +38036,7 @@
         <v>2829</v>
       </c>
       <c r="F1427" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1428" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38064,7 +38056,7 @@
         <v>2830</v>
       </c>
       <c r="F1428" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1429" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38084,7 +38076,7 @@
         <v>2831</v>
       </c>
       <c r="F1429" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1430" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38104,7 +38096,7 @@
         <v>2832</v>
       </c>
       <c r="F1430" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1431" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38124,7 +38116,7 @@
         <v>2833</v>
       </c>
       <c r="F1431" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1432" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38132,7 +38124,7 @@
         <v>1431</v>
       </c>
       <c r="B1432" s="5" t="s">
-        <v>2997</v>
+        <v>2995</v>
       </c>
       <c r="C1432" s="1" t="s">
         <v>1386</v>
@@ -38144,7 +38136,7 @@
         <v>2834</v>
       </c>
       <c r="F1432" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1433" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38164,7 +38156,7 @@
         <v>2835</v>
       </c>
       <c r="F1433" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1434" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38172,7 +38164,7 @@
         <v>1433</v>
       </c>
       <c r="B1434" s="5" t="s">
-        <v>2998</v>
+        <v>2996</v>
       </c>
       <c r="C1434" s="1" t="s">
         <v>1386</v>
@@ -38184,7 +38176,7 @@
         <v>2836</v>
       </c>
       <c r="F1434" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1435" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38192,7 +38184,7 @@
         <v>1434</v>
       </c>
       <c r="B1435" s="5" t="s">
-        <v>2999</v>
+        <v>2997</v>
       </c>
       <c r="C1435" s="1" t="s">
         <v>1386</v>
@@ -38204,7 +38196,7 @@
         <v>2837</v>
       </c>
       <c r="F1435" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1436" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38212,7 +38204,7 @@
         <v>1435</v>
       </c>
       <c r="B1436" s="5" t="s">
-        <v>3000</v>
+        <v>2998</v>
       </c>
       <c r="C1436" s="1" t="s">
         <v>1386</v>
@@ -38224,7 +38216,7 @@
         <v>2838</v>
       </c>
       <c r="F1436" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1437" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38244,7 +38236,7 @@
         <v>2839</v>
       </c>
       <c r="F1437" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1438" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38252,7 +38244,7 @@
         <v>1437</v>
       </c>
       <c r="B1438" s="5" t="s">
-        <v>3001</v>
+        <v>2999</v>
       </c>
       <c r="C1438" s="1" t="s">
         <v>1386</v>
@@ -38264,7 +38256,7 @@
         <v>2840</v>
       </c>
       <c r="F1438" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1439" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38284,7 +38276,7 @@
         <v>2841</v>
       </c>
       <c r="F1439" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1440" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38304,7 +38296,7 @@
         <v>2842</v>
       </c>
       <c r="F1440" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1441" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38324,7 +38316,7 @@
         <v>2843</v>
       </c>
       <c r="F1441" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1442" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38335,7 +38327,7 @@
         <v>1338</v>
       </c>
       <c r="C1442" s="1" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="D1442" s="1" t="s">
         <v>1414</v>
@@ -38344,7 +38336,7 @@
         <v>2844</v>
       </c>
       <c r="F1442" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1443" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38364,7 +38356,7 @@
         <v>2845</v>
       </c>
       <c r="F1443" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1444" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38375,7 +38367,7 @@
         <v>1340</v>
       </c>
       <c r="C1444" s="1" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="D1444" s="1" t="s">
         <v>1409</v>
@@ -38384,7 +38376,7 @@
         <v>2846</v>
       </c>
       <c r="F1444" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1445" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38404,7 +38396,7 @@
         <v>2847</v>
       </c>
       <c r="F1445" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1446" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38424,7 +38416,7 @@
         <v>2848</v>
       </c>
       <c r="F1446" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1447" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38444,7 +38436,7 @@
         <v>2849</v>
       </c>
       <c r="F1447" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1448" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38464,7 +38456,7 @@
         <v>2850</v>
       </c>
       <c r="F1448" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1449" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38472,7 +38464,7 @@
         <v>1448</v>
       </c>
       <c r="B1449" s="5" t="s">
-        <v>3002</v>
+        <v>3000</v>
       </c>
       <c r="C1449" s="1" t="s">
         <v>1386</v>
@@ -38484,7 +38476,7 @@
         <v>2851</v>
       </c>
       <c r="F1449" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1450" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38504,7 +38496,7 @@
         <v>2852</v>
       </c>
       <c r="F1450" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1451" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38524,7 +38516,7 @@
         <v>2853</v>
       </c>
       <c r="F1451" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1452" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38544,7 +38536,7 @@
         <v>2854</v>
       </c>
       <c r="F1452" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1453" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38564,7 +38556,7 @@
         <v>2855</v>
       </c>
       <c r="F1453" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1454" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38584,7 +38576,7 @@
         <v>2856</v>
       </c>
       <c r="F1454" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1455" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38604,7 +38596,7 @@
         <v>2857</v>
       </c>
       <c r="F1455" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1456" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38612,7 +38604,7 @@
         <v>1455</v>
       </c>
       <c r="B1456" s="5" t="s">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="C1456" s="1" t="s">
         <v>1386</v>
@@ -38624,7 +38616,7 @@
         <v>2858</v>
       </c>
       <c r="F1456" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1457" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38644,7 +38636,7 @@
         <v>2859</v>
       </c>
       <c r="F1457" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1458" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38664,7 +38656,7 @@
         <v>2860</v>
       </c>
       <c r="F1458" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1459" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38684,7 +38676,7 @@
         <v>2861</v>
       </c>
       <c r="F1459" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1460" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38704,7 +38696,7 @@
         <v>2862</v>
       </c>
       <c r="F1460" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1461" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38724,7 +38716,7 @@
         <v>2863</v>
       </c>
       <c r="F1461" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1462" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38744,7 +38736,7 @@
         <v>2864</v>
       </c>
       <c r="F1462" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1463" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38764,7 +38756,7 @@
         <v>2865</v>
       </c>
       <c r="F1463" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1464" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38772,7 +38764,7 @@
         <v>1463</v>
       </c>
       <c r="B1464" s="5" t="s">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="C1464" s="1" t="s">
         <v>1386</v>
@@ -38784,7 +38776,7 @@
         <v>2866</v>
       </c>
       <c r="F1464" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1465" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38804,7 +38796,7 @@
         <v>2867</v>
       </c>
       <c r="F1465" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1466" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38824,7 +38816,7 @@
         <v>2868</v>
       </c>
       <c r="F1466" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1467" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38844,7 +38836,7 @@
         <v>2869</v>
       </c>
       <c r="F1467" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1468" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38864,7 +38856,7 @@
         <v>2870</v>
       </c>
       <c r="F1468" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1469" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38884,7 +38876,7 @@
         <v>2871</v>
       </c>
       <c r="F1469" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1470" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38904,7 +38896,7 @@
         <v>2872</v>
       </c>
       <c r="F1470" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1471" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38924,7 +38916,7 @@
         <v>2873</v>
       </c>
       <c r="F1471" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1472" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38932,7 +38924,7 @@
         <v>1471</v>
       </c>
       <c r="B1472" s="5" t="s">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="C1472" s="1" t="s">
         <v>1386</v>
@@ -38944,7 +38936,7 @@
         <v>2874</v>
       </c>
       <c r="F1472" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1473" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38952,7 +38944,7 @@
         <v>1472</v>
       </c>
       <c r="B1473" s="5" t="s">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="C1473" s="1" t="s">
         <v>1386</v>
@@ -38964,7 +38956,7 @@
         <v>2875</v>
       </c>
       <c r="F1473" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1474" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -38984,7 +38976,7 @@
         <v>2876</v>
       </c>
       <c r="F1474" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1475" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39004,7 +38996,7 @@
         <v>2877</v>
       </c>
       <c r="F1475" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1476" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39024,7 +39016,7 @@
         <v>2878</v>
       </c>
       <c r="F1476" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1477" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39044,7 +39036,7 @@
         <v>2879</v>
       </c>
       <c r="F1477" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1478" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39064,7 +39056,7 @@
         <v>2880</v>
       </c>
       <c r="F1478" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1479" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39084,7 +39076,7 @@
         <v>2881</v>
       </c>
       <c r="F1479" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1480" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39104,7 +39096,7 @@
         <v>2882</v>
       </c>
       <c r="F1480" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1481" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39124,7 +39116,7 @@
         <v>2883</v>
       </c>
       <c r="F1481" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1482" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39144,7 +39136,7 @@
         <v>2884</v>
       </c>
       <c r="F1482" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1483" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39164,7 +39156,7 @@
         <v>2885</v>
       </c>
       <c r="F1483" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1484" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39184,7 +39176,7 @@
         <v>2886</v>
       </c>
       <c r="F1484" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1485" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39204,7 +39196,7 @@
         <v>2887</v>
       </c>
       <c r="F1485" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1486" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39224,7 +39216,7 @@
         <v>2888</v>
       </c>
       <c r="F1486" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1487" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39244,7 +39236,7 @@
         <v>2889</v>
       </c>
       <c r="F1487" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1488" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39264,7 +39256,7 @@
         <v>2890</v>
       </c>
       <c r="F1488" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1489" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39284,7 +39276,7 @@
         <v>2891</v>
       </c>
       <c r="F1489" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1490" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39304,7 +39296,7 @@
         <v>2892</v>
       </c>
       <c r="F1490" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1491" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39324,7 +39316,7 @@
         <v>2893</v>
       </c>
       <c r="F1491" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1492" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39335,7 +39327,7 @@
         <v>1383</v>
       </c>
       <c r="C1492" s="1" t="s">
-        <v>2902</v>
+        <v>2900</v>
       </c>
       <c r="D1492" s="1" t="s">
         <v>1412</v>
@@ -39344,7 +39336,7 @@
         <v>2894</v>
       </c>
       <c r="F1492" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1493" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -39364,11 +39356,11 @@
         <v>2895</v>
       </c>
       <c r="F1493" s="1" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I1493" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
